--- a/doc/schemas.xlsx
+++ b/doc/schemas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MSDA\D610 (capstone)\Airport Congestion Prediction System\Task 2\Airport Congestion Prediction System\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C233C58D-D559-4BF2-B5AE-44A5C761434E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B2BA35-ED63-41E1-9CC4-F4B4A892B65E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="10440" windowWidth="26010" windowHeight="10545" firstSheet="3" activeTab="7" xr2:uid="{8D4FF6C1-4669-47F7-9769-3BF49D33B6E0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{8D4FF6C1-4669-47F7-9769-3BF49D33B6E0}"/>
   </bookViews>
   <sheets>
     <sheet name="airport_cleaned" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,6 @@
     <sheet name="airport_congestion_gold" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -308,9 +307,6 @@
     <t>flight_number</t>
   </si>
   <si>
-    <t>hash(year + month + day_of_month + carrier_code + flight_number + origin_airport_code + destination_airport_code + scheduled_elapsed_time)</t>
-  </si>
-  <si>
     <t>passenger_count</t>
   </si>
   <si>
@@ -399,6 +395,9 @@
   </si>
   <si>
     <t>avg_taxi_out_time + avg_taxi_in_time</t>
+  </si>
+  <si>
+    <t>hash(year + month + day_of_month + carrier_code + flight_number + origin_iata_code + destination_iata_code + scheduled_elapsed_time)</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1292,7 @@
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1310,7 +1309,7 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1327,12 +1326,12 @@
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -1349,7 +1348,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -1361,7 +1360,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1378,7 +1377,7 @@
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1395,12 +1394,12 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1412,7 +1411,7 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1451,7 +1450,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
         <v>73</v>
@@ -1468,7 +1467,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
         <v>73</v>
@@ -1553,7 +1552,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -1585,7 +1584,7 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1669,7 +1668,7 @@
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1786,7 +1785,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -1800,7 +1799,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
@@ -2140,6 +2139,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2224,7 +2224,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -2343,7 +2343,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -2632,7 +2632,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
@@ -2644,7 +2644,7 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -2661,12 +2661,12 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
@@ -2678,7 +2678,7 @@
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2857,7 +2857,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -2869,17 +2869,17 @@
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2983,7 +2983,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -3014,7 +3014,7 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -3134,7 +3134,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -3146,12 +3146,12 @@
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -3163,7 +3163,7 @@
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
